--- a/4 четверть_18_JavaScript_pm2.xlsx
+++ b/4 четверть_18_JavaScript_pm2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A360CDE-AB8C-4B9D-9229-C693A58AE4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B49CC6E9-6343-442D-B0FD-17CF3BB99BE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11745" yWindow="-15075" windowWidth="23250" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-13875" yWindow="-21720" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pm2" sheetId="15" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Installation</t>
   </si>
@@ -960,17 +960,84 @@
       <t>package.json</t>
     </r>
   </si>
+  <si>
+    <t>Вызов переменных окружения</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">const tokens = require('./tokens');
+module.exports = {
+  baseURL: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+process.env.AUTH</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ? `http://127.0.0.1:${</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>process.env.AUTH_PORT.trim()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}/api` : `http://10.233.233.110:${process.env.AUTH_PORT.trim()}/api`,
+  timeout: 10000,
+  headers: {'innerauth': 'Server ' + tokens.lk},
+};</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1169,9 +1236,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1182,23 +1249,23 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -1207,41 +1274,47 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{7B23FFB3-A72F-409B-B670-C03B7A66220A}"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1262,14 +1335,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>39124</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>49529</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>3261216</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>2878455</xdr:rowOff>
+      <xdr:colOff>3257406</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>2874645</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1306,14 +1379,14 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>102870</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>4553334</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>2838686</xdr:rowOff>
+      <xdr:colOff>4549524</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>2834876</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1615,7 +1688,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:U116"/>
+  <dimension ref="A2:U118"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -1753,91 +1826,94 @@
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="18"/>
+    </row>
+    <row r="14" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="B14" s="24"/>
+      <c r="C14" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="18"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="18" t="s">
+      <c r="B15" s="15"/>
+      <c r="C15" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="18"/>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="18"/>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A15" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
+      <c r="D15" s="18"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B16" s="15"/>
       <c r="C16" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="18"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="15"/>
+      <c r="C18" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="15"/>
-    </row>
-    <row r="17" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="22" t="s">
+      <c r="D18" s="15"/>
+    </row>
+    <row r="19" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="B19" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C19" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D19" s="22" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="18" t="s">
+    <row r="20" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B19" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="15"/>
-    </row>
-    <row r="20" spans="1:4" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="15"/>
-      <c r="B20" s="22" t="s">
-        <v>23</v>
-      </c>
+      <c r="B20" s="15"/>
       <c r="C20" s="15"/>
       <c r="D20" s="15"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="15"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
+      <c r="B21" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>25</v>
+      </c>
       <c r="D21" s="15"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A22" s="15"/>
-      <c r="B22" s="15"/>
+      <c r="B22" s="22" t="s">
+        <v>23</v>
+      </c>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
     </row>
@@ -1848,6 +1924,7 @@
       <c r="D23" s="15"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="15"/>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
@@ -1859,7 +1936,6 @@
       <c r="D25" s="15"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="15"/>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
       <c r="D26" s="15"/>
@@ -2403,6 +2479,18 @@
       <c r="B116" s="15"/>
       <c r="C116" s="15"/>
       <c r="D116" s="15"/>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117" s="15"/>
+      <c r="B117" s="15"/>
+      <c r="C117" s="15"/>
+      <c r="D117" s="15"/>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A118" s="15"/>
+      <c r="B118" s="15"/>
+      <c r="C118" s="15"/>
+      <c r="D118" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/4 четверть_18_JavaScript_pm2.xlsx
+++ b/4 четверть_18_JavaScript_pm2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B49CC6E9-6343-442D-B0FD-17CF3BB99BE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56D84BB0-51A3-4F5A-A83E-C467ECBAAF4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-13875" yWindow="-21720" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pm2" sheetId="15" r:id="rId1"/>
@@ -593,289 +593,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">pm2 start </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">start/pm2_prod.json
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pm2 save</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-pm2 start </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>prod</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Критически важно знать и помнить!
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">1 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pm2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> нужно дать путь к папке, в которой расположен конфигурационный файл </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>start/pm2_prod.json</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-2 Обращаться по имени pm2 start </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>prod</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> возможно только </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ПОСЛЕ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ЕДИНИЧНОГО</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> запуска с полной командой </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pm2 start</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> start/pm2_prod.json
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">3 При </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>КАЖДОМ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> обновлении конфигурационного файла запуск должен осуществляться по полной команде </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>pm2 start</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>start/pm2_prod.json</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <rPr>
         <b/>
         <sz val="11"/>
@@ -1017,6 +734,383 @@
   timeout: 10000,
   headers: {'innerauth': 'Server ' + tokens.lk},
 };</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Критически важно знать и помнить!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1 Удалить предыдущую конфигурацию/сервер</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">2 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pm2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> нужно дать путь к папке, в которой расположен конфигурационный файл </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>start/pm2_prod.json</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, чтобы по ней создать новый сервер</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+3 Обращаться по имени pm2 start </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>prod</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> возможно только </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ПОСЛЕ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ЕДИНИЧНОГО</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> запуска с полной командой </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pm2 start</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> start/pm2_prod.json
+4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> При </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>КАЖДОМ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> обновлении конфигурационного файла запуск должен осуществляться по полной команде </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pm2 start</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>start/pm2_prod.json</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">pm2 delete </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">auth_server      </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[цифра]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+pm2 start </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">start/pm2_prod.json
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pm2 save
+pm2 dump</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+pm2 start </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>prod</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>не требуется</t>
     </r>
   </si>
 </sst>
@@ -1024,12 +1118,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1180,6 +1282,15 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1236,9 +1347,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1249,23 +1360,23 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -1274,42 +1385,45 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1827,7 +1941,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" s="25" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B13" s="24"/>
       <c r="C13" s="24"/>
@@ -1836,7 +1950,7 @@
     <row r="14" spans="1:21" ht="129.6" x14ac:dyDescent="0.3">
       <c r="B14" s="24"/>
       <c r="C14" s="24" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D14" s="18"/>
     </row>
@@ -1878,18 +1992,18 @@
       </c>
       <c r="D18" s="15"/>
     </row>
-    <row r="19" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="22" t="s">
-        <v>21</v>
+    <row r="19" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>26</v>
       </c>
       <c r="C19" s="21" t="s">
         <v>19</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -1902,17 +2016,17 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B21" s="23" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D21" s="15"/>
     </row>
     <row r="22" spans="1:4" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A22" s="15"/>
       <c r="B22" s="22" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
